--- a/data/trans_orig/IP26C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP26C-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>114144</t>
+          <t>114303</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127038</t>
+          <t>126823</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129513</t>
+          <t>129244</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141047</t>
+          <t>140774</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>249475</t>
+          <t>249195</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>265973</t>
+          <t>265388</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11196</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23875</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20103</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22036</t>
+          <t>22141</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38243</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>158366</t>
+          <t>158956</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173622</t>
+          <t>173682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180087</t>
+          <t>181204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>194817</t>
+          <t>195119</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344575</t>
+          <t>345165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>365064</t>
+          <t>365230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>20587</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>34840</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12719</t>
+          <t>12369</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25728</t>
+          <t>24947</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>36015</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>55156</t>
+          <t>56084</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3608</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119860</t>
+          <t>119875</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>130632</t>
+          <t>130451</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>125847</t>
+          <t>126722</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138267</t>
+          <t>138710</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>250603</t>
+          <t>251091</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>265749</t>
+          <t>266930</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16733</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20710</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>17412</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32724</t>
+          <t>33046</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>176284</t>
+          <t>176140</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>191917</t>
+          <t>192116</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>183521</t>
+          <t>184482</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>196719</t>
+          <t>196433</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>364323</t>
+          <t>366021</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>385237</t>
+          <t>385678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29673</t>
+          <t>29324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23608</t>
+          <t>22647</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28099</t>
+          <t>27888</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48760</t>
+          <t>47320</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>767</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>586422</t>
+          <t>586184</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>613781</t>
+          <t>613347</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>635695</t>
+          <t>634475</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>660419</t>
+          <t>661154</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1229862</t>
+          <t>1230886</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1268979</t>
+          <t>1268681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61995</t>
+          <t>62459</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89184</t>
+          <t>88973</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50902</t>
+          <t>49754</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74007</t>
+          <t>75421</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>117389</t>
+          <t>116898</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>155285</t>
+          <t>153956</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11191</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16413</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115901</t>
+          <t>116186</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128406</t>
+          <t>128096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128808</t>
+          <t>129697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>142539</t>
+          <t>141979</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>248815</t>
+          <t>249148</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>267658</t>
+          <t>267827</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21539</t>
+          <t>20391</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22031</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>21083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38657</t>
+          <t>38781</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181225</t>
+          <t>180638</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>193339</t>
+          <t>193242</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>187102</t>
+          <t>185978</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>202222</t>
+          <t>202168</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>371896</t>
+          <t>371656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>391551</t>
+          <t>391807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10519</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>22858</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18346</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33181</t>
+          <t>34727</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>32871</t>
+          <t>32362</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52348</t>
+          <t>52573</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135059</t>
+          <t>135751</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146207</t>
+          <t>146555</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>141741</t>
+          <t>141283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>153602</t>
+          <t>153320</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>282324</t>
+          <t>281684</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>297109</t>
+          <t>297328</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17904</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20808</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33394</t>
+          <t>34121</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>168016</t>
+          <t>168826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>186304</t>
+          <t>186217</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>174789</t>
+          <t>176038</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189889</t>
+          <t>190654</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>349228</t>
+          <t>349441</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>371736</t>
+          <t>372014</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19504</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37143</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>12508</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26383</t>
+          <t>25825</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36120</t>
+          <t>36303</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57998</t>
+          <t>57440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11190</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>616043</t>
+          <t>615872</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>641650</t>
+          <t>641884</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>648913</t>
+          <t>648420</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>676986</t>
+          <t>676917</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1274500</t>
+          <t>1274265</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1314192</t>
+          <t>1312906</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57540</t>
+          <t>57658</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82091</t>
+          <t>83816</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60985</t>
+          <t>60601</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>88626</t>
+          <t>87046</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>123829</t>
+          <t>124798</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>160296</t>
+          <t>161856</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118689</t>
+          <t>118758</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128481</t>
+          <t>128376</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129218</t>
+          <t>129170</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140333</t>
+          <t>140925</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>252206</t>
+          <t>252414</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>267040</t>
+          <t>266450</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>12429</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17823</t>
+          <t>17855</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12307</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26506</t>
+          <t>25971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179991</t>
+          <t>179532</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>192610</t>
+          <t>192877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195422</t>
+          <t>195685</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209050</t>
+          <t>209186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>380283</t>
+          <t>380111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>399237</t>
+          <t>398648</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21791</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13407</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27035</t>
+          <t>26772</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26360</t>
+          <t>26547</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>44672</t>
+          <t>44125</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>541</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>128564</t>
+          <t>129608</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141634</t>
+          <t>141507</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>141736</t>
+          <t>142117</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>155263</t>
+          <t>154437</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>275847</t>
+          <t>275509</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>293149</t>
+          <t>293263</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21659</t>
+          <t>21511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23554</t>
+          <t>22863</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23161</t>
+          <t>23461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39920</t>
+          <t>40104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9980</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>174746</t>
+          <t>175668</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>190493</t>
+          <t>190852</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>173139</t>
+          <t>173666</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188002</t>
+          <t>187613</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>353760</t>
+          <t>354022</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>375272</t>
+          <t>375080</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>14569</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30404</t>
+          <t>30068</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27505</t>
+          <t>27161</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31132</t>
+          <t>31052</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52648</t>
+          <t>51549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>618748</t>
+          <t>618171</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>643814</t>
+          <t>643296</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>654697</t>
+          <t>655990</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>682042</t>
+          <t>683063</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1282914</t>
+          <t>1283267</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1318549</t>
+          <t>1318282</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47347</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70655</t>
+          <t>73036</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53618</t>
+          <t>52859</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>79651</t>
+          <t>78598</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>108232</t>
+          <t>108170</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>142180</t>
+          <t>142307</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96432</t>
+          <t>96706</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108016</t>
+          <t>108215</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112064</t>
+          <t>111550</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128139</t>
+          <t>128709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>212646</t>
+          <t>212595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>233484</t>
+          <t>233372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>17793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>10931</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27903</t>
+          <t>27818</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21050</t>
+          <t>20671</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40727</t>
+          <t>40530</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160108</t>
+          <t>159784</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>175105</t>
+          <t>174961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210584</t>
+          <t>211453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>231143</t>
+          <t>231757</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>376873</t>
+          <t>377717</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>401712</t>
+          <t>400349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29272</t>
+          <t>29210</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40874</t>
+          <t>40123</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39659</t>
+          <t>40654</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64172</t>
+          <t>63418</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>170917</t>
+          <t>171347</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>183691</t>
+          <t>183418</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167572</t>
+          <t>166799</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>179110</t>
+          <t>179140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>343897</t>
+          <t>343080</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>360274</t>
+          <t>360445</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16209</t>
+          <t>16525</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29803</t>
+          <t>30139</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148345</t>
+          <t>148371</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>159507</t>
+          <t>159293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152488</t>
+          <t>152651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>167834</t>
+          <t>167591</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>305644</t>
+          <t>305145</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>325100</t>
+          <t>324480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17777</t>
+          <t>17747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>28587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>22936</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41360</t>
+          <t>41759</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>590105</t>
+          <t>590672</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>616482</t>
+          <t>616500</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>662807</t>
+          <t>662358</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>694049</t>
+          <t>694501</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1259418</t>
+          <t>1259823</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1301361</t>
+          <t>1302153</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43905</t>
+          <t>43925</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69011</t>
+          <t>69172</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61217</t>
+          <t>62606</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93255</t>
+          <t>94050</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>114326</t>
+          <t>115061</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>155101</t>
+          <t>156359</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>15090</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
